--- a/sample_data/sample-events.xlsx
+++ b/sample_data/sample-events.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19650" windowHeight="17775"/>
+    <workbookView windowWidth="19665" windowHeight="17775"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="33">
   <si>
     <t>Название мероприятия</t>
   </si>
@@ -96,6 +96,15 @@
   </si>
   <si>
     <t>Валидация + создание места</t>
+  </si>
+  <si>
+    <t>2026-04-15T12:00:00</t>
+  </si>
+  <si>
+    <t>2026-04-25T18:00:00</t>
+  </si>
+  <si>
+    <t>2026-04-25T21:00:00</t>
   </si>
   <si>
     <t>Пустынное ранчо</t>
@@ -130,7 +139,7 @@
     <numFmt numFmtId="179" formatCode="_-* #\.##0\ &quot;₽&quot;_-;\-* #\.##0\ &quot;₽&quot;_-;_-* \-\ &quot;₽&quot;_-;_-@_-"/>
     <numFmt numFmtId="180" formatCode="mmm\.yy"/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -140,13 +149,6 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -616,148 +618,148 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1192,22 +1194,22 @@
         <v>22</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="I5" s="1">
         <v>19</v>
@@ -1215,10 +1217,10 @@
     </row>
     <row r="6" s="1" customFormat="1" spans="1:9">
       <c r="A6" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>18</v>
@@ -1230,7 +1232,7 @@
         <v>18</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="G6" s="1" t="s">
         <v>19</v>
@@ -1244,10 +1246,10 @@
     </row>
     <row r="7" s="1" customFormat="1" spans="1:9">
       <c r="A7" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>18</v>
@@ -1259,7 +1261,7 @@
         <v>18</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="G7" s="1" t="s">
         <v>19</v>
